--- a/paper/Tables/TableReg1_log.xlsx
+++ b/paper/Tables/TableReg1_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xps-seira\Dropbox\Apps\ShareLaTeX\information_settlement\Paper\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCLC\Pilot 1\information_sett\ReplicationFinal\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754D2236-D533-4DDA-91ED-B5195DC03A3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF241A85-C6A3-464C-8BB7-67CA501B48A8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22992" windowHeight="8460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-216" yWindow="0" windowWidth="23256" windowHeight="12444" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TableReg1_log" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -199,106 +203,120 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="Reg1_con_log"/>
+      <sheetName val="Reg1_all_log"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="5">
           <cell r="B5" t="str">
-            <v>0.090</v>
+            <v>1.65</v>
           </cell>
           <cell r="D5" t="str">
-            <v>-0.19***</v>
+            <v>0.0011</v>
           </cell>
           <cell r="F5" t="str">
-            <v>-0.67***</v>
+            <v>-0.62***</v>
           </cell>
           <cell r="H5" t="str">
-            <v>0.087***</v>
+            <v>0.055**</v>
           </cell>
         </row>
         <row r="6">
           <cell r="B6" t="str">
-            <v>(0.38)</v>
+            <v>(2.33)</v>
           </cell>
           <cell r="D6" t="str">
-            <v>(0.053)</v>
+            <v>(0.22)</v>
           </cell>
           <cell r="F6" t="str">
-            <v>(0.041)</v>
+            <v>(0.033)</v>
           </cell>
           <cell r="H6" t="str">
-            <v>(0.020)</v>
+            <v>(0.024)</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="B62" t="str">
+            <v/>
+          </cell>
+          <cell r="D62" t="str">
+            <v/>
+          </cell>
+          <cell r="F62" t="str">
+            <v/>
+          </cell>
+          <cell r="H62" t="str">
+            <v/>
           </cell>
         </row>
         <row r="77">
           <cell r="B77" t="str">
-            <v>97.8***</v>
+            <v>75.6***</v>
           </cell>
           <cell r="D77" t="str">
-            <v>6.43***</v>
+            <v>5.48***</v>
           </cell>
           <cell r="F77" t="str">
-            <v>2.63***</v>
+            <v>2.76***</v>
           </cell>
           <cell r="H77" t="str">
-            <v>1.52***</v>
+            <v>1.06***</v>
           </cell>
         </row>
         <row r="78">
           <cell r="B78" t="str">
-            <v>(2.50)</v>
+            <v>(9.67)</v>
           </cell>
           <cell r="D78" t="str">
-            <v>(0.33)</v>
+            <v>(0.97)</v>
           </cell>
           <cell r="F78" t="str">
-            <v>(0.25)</v>
+            <v>(0.19)</v>
           </cell>
           <cell r="H78" t="str">
-            <v>(0.11)</v>
+            <v>(0.10)</v>
           </cell>
         </row>
         <row r="80">
           <cell r="B80" t="str">
-            <v>3081</v>
+            <v>4866</v>
           </cell>
           <cell r="D80" t="str">
-            <v>3080</v>
+            <v>4866</v>
           </cell>
           <cell r="F80" t="str">
-            <v>3081</v>
+            <v>4866</v>
           </cell>
           <cell r="H80" t="str">
-            <v>3080</v>
+            <v>4866</v>
           </cell>
         </row>
         <row r="81">
           <cell r="B81" t="str">
-            <v>0.0065</v>
+            <v>0.020</v>
           </cell>
           <cell r="D81" t="str">
-            <v>0.35</v>
+            <v>0.036</v>
           </cell>
           <cell r="F81" t="str">
             <v>0.74</v>
           </cell>
           <cell r="H81" t="str">
-            <v>0.11</v>
+            <v>0.043</v>
           </cell>
         </row>
         <row r="82">
           <cell r="B82" t="str">
-            <v>99.6</v>
+            <v>65.3</v>
           </cell>
           <cell r="D82" t="str">
-            <v>9.70</v>
+            <v>6.40</v>
           </cell>
           <cell r="F82" t="str">
             <v>11.7</v>
           </cell>
           <cell r="H82" t="str">
-            <v>0.27</v>
+            <v>0.21</v>
           </cell>
         </row>
       </sheetData>
@@ -311,106 +329,106 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="Reg1_lau_log"/>
+      <sheetName val="Reg1_con_log"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="5">
           <cell r="B5" t="str">
-            <v>-0.11</v>
+            <v>0.018</v>
           </cell>
           <cell r="D5" t="str">
-            <v>-0.16</v>
+            <v>-0.20***</v>
           </cell>
           <cell r="F5" t="str">
-            <v>-0.44***</v>
+            <v>-0.67***</v>
           </cell>
           <cell r="H5" t="str">
-            <v>0.039</v>
+            <v>0.087***</v>
           </cell>
         </row>
         <row r="6">
           <cell r="B6" t="str">
-            <v>(7.57)</v>
+            <v>(0.37)</v>
           </cell>
           <cell r="D6" t="str">
-            <v>(0.80)</v>
+            <v>(0.053)</v>
           </cell>
           <cell r="F6" t="str">
-            <v>(0.12)</v>
+            <v>(0.041)</v>
           </cell>
           <cell r="H6" t="str">
-            <v>(0.29)</v>
+            <v>(0.020)</v>
           </cell>
         </row>
         <row r="77">
           <cell r="B77" t="str">
-            <v>-0.29</v>
+            <v>99.4***</v>
           </cell>
           <cell r="D77" t="str">
-            <v>-0.87</v>
+            <v>6.59***</v>
           </cell>
           <cell r="F77" t="str">
-            <v>2.13***</v>
+            <v>2.63***</v>
           </cell>
           <cell r="H77" t="str">
-            <v>1.48**</v>
+            <v>1.52***</v>
           </cell>
         </row>
         <row r="78">
           <cell r="B78" t="str">
-            <v>(26.7)</v>
+            <v>(2.15)</v>
           </cell>
           <cell r="D78" t="str">
-            <v>(2.96)</v>
+            <v>(0.31)</v>
           </cell>
           <cell r="F78" t="str">
-            <v>(0.70)</v>
+            <v>(0.25)</v>
           </cell>
           <cell r="H78" t="str">
-            <v>(0.75)</v>
+            <v>(0.11)</v>
           </cell>
         </row>
         <row r="80">
           <cell r="B80" t="str">
-            <v>417</v>
+            <v>3077</v>
           </cell>
           <cell r="D80" t="str">
-            <v>416</v>
+            <v>3077</v>
           </cell>
           <cell r="F80" t="str">
-            <v>417</v>
+            <v>3077</v>
           </cell>
           <cell r="H80" t="str">
-            <v>416</v>
+            <v>3077</v>
           </cell>
         </row>
         <row r="81">
           <cell r="B81" t="str">
-            <v>0.13</v>
+            <v>0.0068</v>
           </cell>
           <cell r="D81" t="str">
-            <v>0.13</v>
+            <v>0.37</v>
           </cell>
           <cell r="F81" t="str">
-            <v>0.78</v>
+            <v>0.74</v>
           </cell>
           <cell r="H81" t="str">
-            <v>0.056</v>
+            <v>0.11</v>
           </cell>
         </row>
         <row r="82">
           <cell r="B82" t="str">
-            <v>23.8</v>
+            <v>99.6</v>
           </cell>
           <cell r="D82" t="str">
-            <v>2.67</v>
+            <v>9.70</v>
           </cell>
           <cell r="F82" t="str">
             <v>11.7</v>
           </cell>
           <cell r="H82" t="str">
-            <v>0.34</v>
+            <v>0.27</v>
           </cell>
         </row>
       </sheetData>
@@ -423,120 +441,106 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="Reg1_all_log"/>
+      <sheetName val="Reg1_lau_log"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="5">
           <cell r="B5" t="str">
-            <v>1.67</v>
+            <v>-0.59</v>
           </cell>
           <cell r="D5" t="str">
-            <v>0.0049</v>
+            <v>-0.22</v>
           </cell>
           <cell r="F5" t="str">
-            <v>-0.62***</v>
+            <v>-0.44***</v>
           </cell>
           <cell r="H5" t="str">
-            <v>0.057**</v>
+            <v>0.027</v>
           </cell>
         </row>
         <row r="6">
           <cell r="B6" t="str">
-            <v>(2.33)</v>
+            <v>(7.59)</v>
           </cell>
           <cell r="D6" t="str">
-            <v>(0.22)</v>
+            <v>(0.81)</v>
           </cell>
           <cell r="F6" t="str">
-            <v>(0.033)</v>
+            <v>(0.12)</v>
           </cell>
           <cell r="H6" t="str">
-            <v>(0.024)</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="B62" t="str">
-            <v/>
-          </cell>
-          <cell r="D62" t="str">
-            <v/>
-          </cell>
-          <cell r="F62" t="str">
-            <v/>
-          </cell>
-          <cell r="H62" t="str">
-            <v/>
+            <v>(0.29)</v>
           </cell>
         </row>
         <row r="77">
           <cell r="B77" t="str">
-            <v>74.4***</v>
+            <v>7.23</v>
           </cell>
           <cell r="D77" t="str">
-            <v>5.33***</v>
+            <v>0.63</v>
           </cell>
           <cell r="F77" t="str">
-            <v>2.76***</v>
+            <v>2.14***</v>
           </cell>
           <cell r="H77" t="str">
-            <v>1.02***</v>
+            <v>1.86**</v>
           </cell>
         </row>
         <row r="78">
           <cell r="B78" t="str">
-            <v>(9.67)</v>
+            <v>(27.5)</v>
           </cell>
           <cell r="D78" t="str">
-            <v>(0.97)</v>
+            <v>(3.14)</v>
           </cell>
           <cell r="F78" t="str">
-            <v>(0.19)</v>
+            <v>(0.68)</v>
           </cell>
           <cell r="H78" t="str">
-            <v>(0.095)</v>
+            <v>(0.84)</v>
           </cell>
         </row>
         <row r="80">
           <cell r="B80" t="str">
-            <v>4866</v>
+            <v>422</v>
           </cell>
           <cell r="D80" t="str">
-            <v>4864</v>
+            <v>422</v>
           </cell>
           <cell r="F80" t="str">
-            <v>4866</v>
+            <v>422</v>
           </cell>
           <cell r="H80" t="str">
-            <v>4864</v>
+            <v>422</v>
           </cell>
         </row>
         <row r="81">
           <cell r="B81" t="str">
-            <v>0.020</v>
+            <v>0.13</v>
           </cell>
           <cell r="D81" t="str">
-            <v>0.036</v>
+            <v>0.13</v>
           </cell>
           <cell r="F81" t="str">
-            <v>0.74</v>
+            <v>0.78</v>
           </cell>
           <cell r="H81" t="str">
-            <v>0.042</v>
+            <v>0.065</v>
           </cell>
         </row>
         <row r="82">
           <cell r="B82" t="str">
-            <v>65.3</v>
+            <v>24.2</v>
           </cell>
           <cell r="D82" t="str">
-            <v>6.39</v>
+            <v>2.74</v>
           </cell>
           <cell r="F82" t="str">
             <v>11.7</v>
           </cell>
           <cell r="H82" t="str">
-            <v>0.20</v>
+            <v>0.37</v>
           </cell>
         </row>
       </sheetData>
@@ -546,7 +550,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -843,7 +847,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A10:E48"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
@@ -874,37 +878,37 @@
         <v>4</v>
       </c>
       <c r="B12" s="4" t="str">
-        <f>[3]Reg1_all_log!F5</f>
+        <f>[1]Reg1_all_log!F5</f>
         <v>-0.62***</v>
       </c>
       <c r="C12" s="4" t="str">
-        <f>[3]Reg1_all_log!D5</f>
-        <v>0.0049</v>
+        <f>[1]Reg1_all_log!D5</f>
+        <v>0.0011</v>
       </c>
       <c r="D12" s="4" t="str">
-        <f>[3]Reg1_all_log!H5</f>
-        <v>0.057**</v>
+        <f>[1]Reg1_all_log!H5</f>
+        <v>0.055**</v>
       </c>
       <c r="E12" s="4" t="str">
-        <f>[3]Reg1_all_log!B5</f>
-        <v>1.67</v>
+        <f>[1]Reg1_all_log!B5</f>
+        <v>1.65</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="str">
-        <f>[3]Reg1_all_log!F6</f>
+        <f>[1]Reg1_all_log!F6</f>
         <v>(0.033)</v>
       </c>
       <c r="C13" s="4" t="str">
-        <f>[3]Reg1_all_log!D6</f>
+        <f>[1]Reg1_all_log!D6</f>
         <v>(0.22)</v>
       </c>
       <c r="D13" s="4" t="str">
-        <f>[3]Reg1_all_log!H6</f>
+        <f>[1]Reg1_all_log!H6</f>
         <v>(0.024)</v>
       </c>
       <c r="E13" s="4" t="str">
-        <f>[3]Reg1_all_log!B6</f>
+        <f>[1]Reg1_all_log!B6</f>
         <v>(2.33)</v>
       </c>
     </row>
@@ -913,55 +917,55 @@
         <v>5</v>
       </c>
       <c r="B14" s="4" t="str">
-        <f>[3]Reg1_all_log!F77</f>
+        <f>[1]Reg1_all_log!F77</f>
         <v>2.76***</v>
       </c>
       <c r="C14" s="4" t="str">
-        <f>[3]Reg1_all_log!D77</f>
-        <v>5.33***</v>
+        <f>[1]Reg1_all_log!D77</f>
+        <v>5.48***</v>
       </c>
       <c r="D14" s="4" t="str">
-        <f>[3]Reg1_all_log!H77</f>
-        <v>1.02***</v>
+        <f>[1]Reg1_all_log!H77</f>
+        <v>1.06***</v>
       </c>
       <c r="E14" s="4" t="str">
-        <f>[3]Reg1_all_log!B77</f>
-        <v>74.4***</v>
+        <f>[1]Reg1_all_log!B77</f>
+        <v>75.6***</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="str">
-        <f>[3]Reg1_all_log!F78</f>
+        <f>[1]Reg1_all_log!F78</f>
         <v>(0.19)</v>
       </c>
       <c r="C15" s="4" t="str">
-        <f>[3]Reg1_all_log!D78</f>
+        <f>[1]Reg1_all_log!D78</f>
         <v>(0.97)</v>
       </c>
       <c r="D15" s="4" t="str">
-        <f>[3]Reg1_all_log!H78</f>
-        <v>(0.095)</v>
+        <f>[1]Reg1_all_log!H78</f>
+        <v>(0.10)</v>
       </c>
       <c r="E15" s="4" t="str">
-        <f>[3]Reg1_all_log!B78</f>
+        <f>[1]Reg1_all_log!B78</f>
         <v>(9.67)</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="str">
-        <f>[3]Reg1_all_log!F62</f>
+        <f>[1]Reg1_all_log!F62</f>
         <v/>
       </c>
       <c r="C16" s="4" t="str">
-        <f>[3]Reg1_all_log!D62</f>
+        <f>[1]Reg1_all_log!D62</f>
         <v/>
       </c>
       <c r="D16" s="4" t="str">
-        <f>[3]Reg1_all_log!H62</f>
+        <f>[1]Reg1_all_log!H62</f>
         <v/>
       </c>
       <c r="E16" s="4" t="str">
-        <f>[3]Reg1_all_log!B62</f>
+        <f>[1]Reg1_all_log!B62</f>
         <v/>
       </c>
     </row>
@@ -970,19 +974,19 @@
         <v>6</v>
       </c>
       <c r="B17" s="3" t="str">
-        <f>[3]Reg1_all_log!F80</f>
+        <f>[1]Reg1_all_log!F80</f>
         <v>4866</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f>[3]Reg1_all_log!D80</f>
-        <v>4864</v>
+        <f>[1]Reg1_all_log!D80</f>
+        <v>4866</v>
       </c>
       <c r="D17" s="3" t="str">
-        <f>[3]Reg1_all_log!H80</f>
-        <v>4864</v>
+        <f>[1]Reg1_all_log!H80</f>
+        <v>4866</v>
       </c>
       <c r="E17" s="3" t="str">
-        <f>[3]Reg1_all_log!B80</f>
+        <f>[1]Reg1_all_log!B80</f>
         <v>4866</v>
       </c>
     </row>
@@ -1025,19 +1029,19 @@
         <v>9</v>
       </c>
       <c r="B20" s="4" t="str">
-        <f>[3]Reg1_all_log!F81</f>
+        <f>[1]Reg1_all_log!F81</f>
         <v>0.74</v>
       </c>
       <c r="C20" s="4" t="str">
-        <f>[3]Reg1_all_log!D81</f>
+        <f>[1]Reg1_all_log!D81</f>
         <v>0.036</v>
       </c>
       <c r="D20" s="4" t="str">
-        <f>[3]Reg1_all_log!H81</f>
-        <v>0.042</v>
+        <f>[1]Reg1_all_log!H81</f>
+        <v>0.043</v>
       </c>
       <c r="E20" s="4" t="str">
-        <f>[3]Reg1_all_log!B81</f>
+        <f>[1]Reg1_all_log!B81</f>
         <v>0.020</v>
       </c>
     </row>
@@ -1046,19 +1050,19 @@
         <v>10</v>
       </c>
       <c r="B21" s="7" t="str">
-        <f>[3]Reg1_all_log!F82</f>
+        <f>[1]Reg1_all_log!F82</f>
         <v>11.7</v>
       </c>
       <c r="C21" s="7" t="str">
-        <f>[3]Reg1_all_log!D82</f>
-        <v>6.39</v>
+        <f>[1]Reg1_all_log!D82</f>
+        <v>6.40</v>
       </c>
       <c r="D21" s="7" t="str">
-        <f>[3]Reg1_all_log!H82</f>
-        <v>0.20</v>
+        <f>[1]Reg1_all_log!H82</f>
+        <v>0.21</v>
       </c>
       <c r="E21" s="7" t="str">
-        <f>[3]Reg1_all_log!B82</f>
+        <f>[1]Reg1_all_log!B82</f>
         <v>65.3</v>
       </c>
     </row>
@@ -1092,38 +1096,38 @@
         <v>4</v>
       </c>
       <c r="B25" s="4" t="str">
-        <f>[1]Reg1_con_log!F5</f>
+        <f>[2]Reg1_con_log!F5</f>
         <v>-0.67***</v>
       </c>
       <c r="C25" s="4" t="str">
-        <f>[1]Reg1_con_log!D5</f>
-        <v>-0.19***</v>
+        <f>[2]Reg1_con_log!D5</f>
+        <v>-0.20***</v>
       </c>
       <c r="D25" s="4" t="str">
-        <f>[1]Reg1_con_log!H5</f>
+        <f>[2]Reg1_con_log!H5</f>
         <v>0.087***</v>
       </c>
       <c r="E25" s="4" t="str">
-        <f>[1]Reg1_con_log!B5</f>
-        <v>0.090</v>
+        <f>[2]Reg1_con_log!B5</f>
+        <v>0.018</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="str">
-        <f>[1]Reg1_con_log!F6</f>
+        <f>[2]Reg1_con_log!F6</f>
         <v>(0.041)</v>
       </c>
       <c r="C26" s="4" t="str">
-        <f>[1]Reg1_con_log!D6</f>
+        <f>[2]Reg1_con_log!D6</f>
         <v>(0.053)</v>
       </c>
       <c r="D26" s="4" t="str">
-        <f>[1]Reg1_con_log!H6</f>
+        <f>[2]Reg1_con_log!H6</f>
         <v>(0.020)</v>
       </c>
       <c r="E26" s="4" t="str">
-        <f>[1]Reg1_con_log!B6</f>
-        <v>(0.38)</v>
+        <f>[2]Reg1_con_log!B6</f>
+        <v>(0.37)</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1131,38 +1135,38 @@
         <v>5</v>
       </c>
       <c r="B27" s="4" t="str">
-        <f>[1]Reg1_con_log!F77</f>
+        <f>[2]Reg1_con_log!F77</f>
         <v>2.63***</v>
       </c>
       <c r="C27" s="4" t="str">
-        <f>[1]Reg1_con_log!D77</f>
-        <v>6.43***</v>
+        <f>[2]Reg1_con_log!D77</f>
+        <v>6.59***</v>
       </c>
       <c r="D27" s="4" t="str">
-        <f>[1]Reg1_con_log!H77</f>
+        <f>[2]Reg1_con_log!H77</f>
         <v>1.52***</v>
       </c>
       <c r="E27" s="4" t="str">
-        <f>[1]Reg1_con_log!B77</f>
-        <v>97.8***</v>
+        <f>[2]Reg1_con_log!B77</f>
+        <v>99.4***</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="str">
-        <f>[1]Reg1_con_log!F78</f>
+        <f>[2]Reg1_con_log!F78</f>
         <v>(0.25)</v>
       </c>
       <c r="C28" s="4" t="str">
-        <f>[1]Reg1_con_log!D78</f>
-        <v>(0.33)</v>
+        <f>[2]Reg1_con_log!D78</f>
+        <v>(0.31)</v>
       </c>
       <c r="D28" s="4" t="str">
-        <f>[1]Reg1_con_log!H78</f>
+        <f>[2]Reg1_con_log!H78</f>
         <v>(0.11)</v>
       </c>
       <c r="E28" s="4" t="str">
-        <f>[1]Reg1_con_log!B78</f>
-        <v>(2.50)</v>
+        <f>[2]Reg1_con_log!B78</f>
+        <v>(2.15)</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1176,20 +1180,20 @@
         <v>6</v>
       </c>
       <c r="B30" s="3" t="str">
-        <f>[1]Reg1_con_log!F80</f>
-        <v>3081</v>
+        <f>[2]Reg1_con_log!F80</f>
+        <v>3077</v>
       </c>
       <c r="C30" s="3" t="str">
-        <f>[1]Reg1_con_log!D80</f>
-        <v>3080</v>
+        <f>[2]Reg1_con_log!D80</f>
+        <v>3077</v>
       </c>
       <c r="D30" s="3" t="str">
-        <f>[1]Reg1_con_log!H80</f>
-        <v>3080</v>
+        <f>[2]Reg1_con_log!H80</f>
+        <v>3077</v>
       </c>
       <c r="E30" s="3" t="str">
-        <f>[1]Reg1_con_log!B80</f>
-        <v>3081</v>
+        <f>[2]Reg1_con_log!B80</f>
+        <v>3077</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1231,20 +1235,20 @@
         <v>9</v>
       </c>
       <c r="B33" s="4" t="str">
-        <f>[1]Reg1_con_log!F81</f>
+        <f>[2]Reg1_con_log!F81</f>
         <v>0.74</v>
       </c>
       <c r="C33" s="4" t="str">
-        <f>[1]Reg1_con_log!D81</f>
-        <v>0.35</v>
+        <f>[2]Reg1_con_log!D81</f>
+        <v>0.37</v>
       </c>
       <c r="D33" s="4" t="str">
-        <f>[1]Reg1_con_log!H81</f>
+        <f>[2]Reg1_con_log!H81</f>
         <v>0.11</v>
       </c>
       <c r="E33" s="4" t="str">
-        <f>[1]Reg1_con_log!B81</f>
-        <v>0.0065</v>
+        <f>[2]Reg1_con_log!B81</f>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1252,19 +1256,19 @@
         <v>10</v>
       </c>
       <c r="B34" s="6" t="str">
-        <f>[1]Reg1_con_log!F82</f>
+        <f>[2]Reg1_con_log!F82</f>
         <v>11.7</v>
       </c>
       <c r="C34" s="6" t="str">
-        <f>[1]Reg1_con_log!D82</f>
+        <f>[2]Reg1_con_log!D82</f>
         <v>9.70</v>
       </c>
       <c r="D34" s="6" t="str">
-        <f>[1]Reg1_con_log!H82</f>
+        <f>[2]Reg1_con_log!H82</f>
         <v>0.27</v>
       </c>
       <c r="E34" s="7" t="str">
-        <f>[1]Reg1_con_log!B82</f>
+        <f>[2]Reg1_con_log!B82</f>
         <v>99.6</v>
       </c>
     </row>
@@ -1298,39 +1302,39 @@
         <v>4</v>
       </c>
       <c r="B38" s="8" t="str">
-        <f>[2]Reg1_lau_log!F5</f>
+        <f>[3]Reg1_lau_log!F5</f>
         <v>-0.44***</v>
       </c>
       <c r="C38" s="4" t="str">
-        <f>[2]Reg1_lau_log!D5</f>
-        <v>-0.16</v>
+        <f>[3]Reg1_lau_log!D5</f>
+        <v>-0.22</v>
       </c>
       <c r="D38" s="4" t="str">
-        <f>[2]Reg1_lau_log!H5</f>
-        <v>0.039</v>
+        <f>[3]Reg1_lau_log!H5</f>
+        <v>0.027</v>
       </c>
       <c r="E38" s="4" t="str">
-        <f>[2]Reg1_lau_log!B5</f>
-        <v>-0.11</v>
+        <f>[3]Reg1_lau_log!B5</f>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="8" t="str">
-        <f>[2]Reg1_lau_log!F6</f>
+        <f>[3]Reg1_lau_log!F6</f>
         <v>(0.12)</v>
       </c>
       <c r="C39" s="4" t="str">
-        <f>[2]Reg1_lau_log!D6</f>
-        <v>(0.80)</v>
+        <f>[3]Reg1_lau_log!D6</f>
+        <v>(0.81)</v>
       </c>
       <c r="D39" s="4" t="str">
-        <f>[2]Reg1_lau_log!H6</f>
+        <f>[3]Reg1_lau_log!H6</f>
         <v>(0.29)</v>
       </c>
       <c r="E39" s="4" t="str">
-        <f>[2]Reg1_lau_log!B6</f>
-        <v>(7.57)</v>
+        <f>[3]Reg1_lau_log!B6</f>
+        <v>(7.59)</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1338,39 +1342,39 @@
         <v>5</v>
       </c>
       <c r="B40" s="8" t="str">
-        <f>[2]Reg1_lau_log!F77</f>
-        <v>2.13***</v>
+        <f>[3]Reg1_lau_log!F77</f>
+        <v>2.14***</v>
       </c>
       <c r="C40" s="4" t="str">
-        <f>[2]Reg1_lau_log!D77</f>
-        <v>-0.87</v>
+        <f>[3]Reg1_lau_log!D77</f>
+        <v>0.63</v>
       </c>
       <c r="D40" s="4" t="str">
-        <f>[2]Reg1_lau_log!H77</f>
-        <v>1.48**</v>
+        <f>[3]Reg1_lau_log!H77</f>
+        <v>1.86**</v>
       </c>
       <c r="E40" s="4" t="str">
-        <f>[2]Reg1_lau_log!B77</f>
-        <v>-0.29</v>
+        <f>[3]Reg1_lau_log!B77</f>
+        <v>7.23</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="8" t="str">
-        <f>[2]Reg1_lau_log!F78</f>
-        <v>(0.70)</v>
+        <f>[3]Reg1_lau_log!F78</f>
+        <v>(0.68)</v>
       </c>
       <c r="C41" s="4" t="str">
-        <f>[2]Reg1_lau_log!D78</f>
-        <v>(2.96)</v>
+        <f>[3]Reg1_lau_log!D78</f>
+        <v>(3.14)</v>
       </c>
       <c r="D41" s="4" t="str">
-        <f>[2]Reg1_lau_log!H78</f>
-        <v>(0.75)</v>
+        <f>[3]Reg1_lau_log!H78</f>
+        <v>(0.84)</v>
       </c>
       <c r="E41" s="4" t="str">
-        <f>[2]Reg1_lau_log!B78</f>
-        <v>(26.7)</v>
+        <f>[3]Reg1_lau_log!B78</f>
+        <v>(27.5)</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1385,20 +1389,20 @@
         <v>6</v>
       </c>
       <c r="B43" s="3" t="str">
-        <f>[2]Reg1_lau_log!F80</f>
-        <v>417</v>
+        <f>[3]Reg1_lau_log!F80</f>
+        <v>422</v>
       </c>
       <c r="C43" s="3" t="str">
-        <f>[2]Reg1_lau_log!D80</f>
-        <v>416</v>
+        <f>[3]Reg1_lau_log!D80</f>
+        <v>422</v>
       </c>
       <c r="D43" s="3" t="str">
-        <f>[2]Reg1_lau_log!H80</f>
-        <v>416</v>
+        <f>[3]Reg1_lau_log!H80</f>
+        <v>422</v>
       </c>
       <c r="E43" s="3" t="str">
-        <f>[2]Reg1_lau_log!B80</f>
-        <v>417</v>
+        <f>[3]Reg1_lau_log!B80</f>
+        <v>422</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1440,19 +1444,19 @@
         <v>9</v>
       </c>
       <c r="B46" s="8" t="str">
-        <f>[2]Reg1_lau_log!F81</f>
+        <f>[3]Reg1_lau_log!F81</f>
         <v>0.78</v>
       </c>
       <c r="C46" s="4" t="str">
-        <f>[2]Reg1_lau_log!D81</f>
+        <f>[3]Reg1_lau_log!D81</f>
         <v>0.13</v>
       </c>
       <c r="D46" s="4" t="str">
-        <f>[2]Reg1_lau_log!H81</f>
-        <v>0.056</v>
+        <f>[3]Reg1_lau_log!H81</f>
+        <v>0.065</v>
       </c>
       <c r="E46" s="4" t="str">
-        <f>[2]Reg1_lau_log!B81</f>
+        <f>[3]Reg1_lau_log!B81</f>
         <v>0.13</v>
       </c>
     </row>
@@ -1461,20 +1465,20 @@
         <v>10</v>
       </c>
       <c r="B47" s="7" t="str">
-        <f>[2]Reg1_lau_log!F82</f>
+        <f>[3]Reg1_lau_log!F82</f>
         <v>11.7</v>
       </c>
       <c r="C47" s="6" t="str">
-        <f>[2]Reg1_lau_log!D82</f>
-        <v>2.67</v>
+        <f>[3]Reg1_lau_log!D82</f>
+        <v>2.74</v>
       </c>
       <c r="D47" s="6" t="str">
-        <f>[2]Reg1_lau_log!H82</f>
-        <v>0.34</v>
+        <f>[3]Reg1_lau_log!H82</f>
+        <v>0.37</v>
       </c>
       <c r="E47" s="6" t="str">
-        <f>[2]Reg1_lau_log!B82</f>
-        <v>23.8</v>
+        <f>[3]Reg1_lau_log!B82</f>
+        <v>24.2</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
